--- a/diagrama de gantt.xlsx
+++ b/diagrama de gantt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\IDEA-PROYECTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF0A896C-C818-4B78-8ABF-529E26C44254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CEB896B-BDD9-40AD-AB4A-0AB3E7558C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/diagrama de gantt.xlsx
+++ b/diagrama de gantt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\IDEA-PROYECTO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\IDEA-PROYECTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CEB896B-BDD9-40AD-AB4A-0AB3E7558C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4A67AC-07A6-4201-A7D3-39368281C261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -314,7 +314,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="es-MX"/>
+          <a:endParaRPr lang="es-PE"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -389,25 +389,25 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>45901</c:v>
+                  <c:v>46113</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>45908</c:v>
+                  <c:v>46120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>45915</c:v>
+                  <c:v>46127</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>45922</c:v>
+                  <c:v>46134</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>45929</c:v>
+                  <c:v>46141</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>45936</c:v>
+                  <c:v>46148</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>45943</c:v>
+                  <c:v>46155</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -455,7 +455,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="es-MX"/>
+                <a:endParaRPr lang="es-PE"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="ctr"/>
@@ -648,7 +648,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-MX"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="509319855"/>
@@ -662,8 +662,8 @@
         <c:axId val="509319855"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="45949"/>
-          <c:min val="45901"/>
+          <c:max val="46161"/>
+          <c:min val="46113"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="t"/>
@@ -723,7 +723,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-MX"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="419159951"/>
@@ -772,7 +772,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="es-MX"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1671,13 +1671,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="14">
-        <v>45901</v>
+        <v>46113</v>
       </c>
       <c r="D3" s="13">
         <v>7</v>
       </c>
       <c r="E3" s="14">
-        <v>45907</v>
+        <v>46119</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>8</v>
@@ -1691,13 +1691,13 @@
         <v>10</v>
       </c>
       <c r="C4" s="14">
-        <v>45908</v>
+        <v>46120</v>
       </c>
       <c r="D4" s="13">
         <v>7</v>
       </c>
       <c r="E4" s="14">
-        <v>45914</v>
+        <v>46126</v>
       </c>
       <c r="F4" s="13" t="s">
         <v>11</v>
@@ -1711,13 +1711,13 @@
         <v>13</v>
       </c>
       <c r="C5" s="14">
-        <v>45915</v>
+        <v>46127</v>
       </c>
       <c r="D5" s="13">
         <v>7</v>
       </c>
       <c r="E5" s="14">
-        <v>45921</v>
+        <v>46133</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>14</v>
@@ -1731,13 +1731,13 @@
         <v>16</v>
       </c>
       <c r="C6" s="14">
-        <v>45922</v>
+        <v>46134</v>
       </c>
       <c r="D6" s="13">
         <v>7</v>
       </c>
       <c r="E6" s="14">
-        <v>45928</v>
+        <v>46140</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>17</v>
@@ -1751,13 +1751,13 @@
         <v>19</v>
       </c>
       <c r="C7" s="14">
-        <v>45929</v>
+        <v>46141</v>
       </c>
       <c r="D7" s="13">
         <v>7</v>
       </c>
       <c r="E7" s="14">
-        <v>45935</v>
+        <v>46147</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>20</v>
@@ -1771,13 +1771,13 @@
         <v>22</v>
       </c>
       <c r="C8" s="14">
-        <v>45936</v>
+        <v>46148</v>
       </c>
       <c r="D8" s="13">
         <v>7</v>
       </c>
       <c r="E8" s="14">
-        <v>45942</v>
+        <v>46154</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>23</v>
@@ -1791,13 +1791,13 @@
         <v>25</v>
       </c>
       <c r="C9" s="14">
-        <v>45943</v>
+        <v>46155</v>
       </c>
       <c r="D9" s="13">
         <v>7</v>
       </c>
       <c r="E9" s="14">
-        <v>45949</v>
+        <v>46161</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>26</v>
